--- a/src/data/opportunity_pool.xlsx
+++ b/src/data/opportunity_pool.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\githubPlaywright\Digitar\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kareem_mohamed/Documents/Digitar/src/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECD4FDD-2B32-4206-B617-12AD312C9256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FB7060-475D-F645-9354-F0D74CD06B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D4274522-4FC5-AA4D-9454-1960407F4585}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15840" xr2:uid="{D4274522-4FC5-AA4D-9454-1960407F4585}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$90</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="13">
   <si>
     <t>intent_interpretation</t>
   </si>
@@ -75,7 +77,7 @@
     <t>City</t>
   </si>
   <si>
-    <t>Automation Project Offplan 20261018083235</t>
+    <t>الرياض التحالف العقارية إشراق ليفنج</t>
   </si>
 </sst>
 </file>
@@ -99,7 +101,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -160,17 +162,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -187,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -211,10 +202,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -222,6 +210,22 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -316,21 +320,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -402,16 +391,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{153B2018-CD67-3049-BF85-9726A69CDA3E}" name="Table1" displayName="Table1" ref="A1:G16" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G16" xr:uid="{2776510C-6183-414D-8B9F-0787CF84E247}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{153B2018-CD67-3049-BF85-9726A69CDA3E}" name="Table1" displayName="Table1" ref="A1:G90" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:G90" xr:uid="{2776510C-6183-414D-8B9F-0787CF84E247}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D72FCA3B-0E3D-EC4E-BCC1-126718FAC54F}" name="Opportunity reference number" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{4EED5066-4028-FA44-8918-8E86851AF50E}" name="Customer name" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{F175C1D6-A9DE-46B9-B27A-023E174F73C7}" name="Customer ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{31D22927-C519-D84C-BB72-E7A018CCEEAD}" name="Phone number" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{0AAA3593-A219-194A-8DE1-15B95B61BDF5}" name="Project name" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{BA3ADE79-7B75-7F41-AD52-4D2A407817A9}" name="City" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{B72E32AB-339B-0F4F-9871-985A40799B36}" name="intent_interpretation" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D72FCA3B-0E3D-EC4E-BCC1-126718FAC54F}" name="Opportunity reference number" dataDxfId="0">
+      <calculatedColumnFormula>RANDBETWEEN(100000,2000000)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{4EED5066-4028-FA44-8918-8E86851AF50E}" name="Customer name" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{F175C1D6-A9DE-46B9-B27A-023E174F73C7}" name="Customer ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{31D22927-C519-D84C-BB72-E7A018CCEEAD}" name="Phone number" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{0AAA3593-A219-194A-8DE1-15B95B61BDF5}" name="Project name" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{BA3ADE79-7B75-7F41-AD52-4D2A407817A9}" name="City" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{B72E32AB-339B-0F4F-9871-985A40799B36}" name="intent_interpretation" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -734,18 +725,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2776510C-6183-414D-8B9F-0787CF84E247}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G90"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.5" customWidth="1"/>
     <col min="4" max="4" width="15.5" style="7" customWidth="1"/>
-    <col min="5" max="5" width="69.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="69.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="44.5" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -768,9 +759,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>1619453</v>
+        <f ca="1">RANDBETWEEN(100000,2000000)</f>
+        <v>991512</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
@@ -783,15 +775,16 @@
         <v>12</v>
       </c>
       <c r="F2" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
-        <v>7747643</v>
+        <f t="shared" ref="A3:A66" ca="1" si="0">RANDBETWEEN(100000,2000000)</f>
+        <v>549433</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>6</v>
@@ -804,15 +797,16 @@
         <v>12</v>
       </c>
       <c r="F3" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>1329887</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>352239</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>7</v>
@@ -825,15 +819,16 @@
         <v>12</v>
       </c>
       <c r="F4" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>774764</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1438910</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>6</v>
@@ -846,133 +841,140 @@
         <v>12</v>
       </c>
       <c r="F5" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>1329889</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>933605</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>966526536272</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="9">
-        <v>1</v>
-      </c>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F6" s="4">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
-        <v>1329888</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1776600</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>966524536272</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>1440912</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1105622</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>966524226272</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>155193</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>670654</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>966542262722</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <v>1662962</v>
-      </c>
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>596985</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>966543222722</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>1773987</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1425340</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>966542232722</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>1885012</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>121576</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>966523212722</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -983,81 +985,1565 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>1996036</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1333424</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>966542636222</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
-        <v>2107061</v>
-      </c>
-      <c r="B14" s="9" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>371809</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>966542223322</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F14" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>2218086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>918953</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>966542243322</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>2329111</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1404722</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>966542232326</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1485289</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>799696</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="4">
+        <v>2</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>470977</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="4">
+        <v>2</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1880457</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="4">
+        <v>2</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1500899</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="4">
+        <v>2</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>896506</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="4">
+        <v>2</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>484912</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="4">
+        <v>2</v>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1847844</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="4">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>819887</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="4">
+        <v>2</v>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1554029</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="4">
+        <v>2</v>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1829539</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="4">
+        <v>2</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>692644</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="4">
+        <v>2</v>
+      </c>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1467146</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="4">
+        <v>2</v>
+      </c>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>590023</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="4">
+        <v>2</v>
+      </c>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>666075</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="4">
+        <v>2</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>646806</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="4">
+        <v>2</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>561930</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="4">
+        <v>2</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>422035</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="4">
+        <v>2</v>
+      </c>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>164819</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="4">
+        <v>2</v>
+      </c>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>252293</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="4">
+        <v>2</v>
+      </c>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>139568</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="4">
+        <v>2</v>
+      </c>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>772228</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="4">
+        <v>2</v>
+      </c>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>880036</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="4">
+        <v>2</v>
+      </c>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>406333</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="4">
+        <v>2</v>
+      </c>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>234692</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="4">
+        <v>2</v>
+      </c>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>230208</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="4">
+        <v>2</v>
+      </c>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>346166</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="4">
+        <v>2</v>
+      </c>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>901873</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="4">
+        <v>2</v>
+      </c>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1935367</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="4">
+        <v>2</v>
+      </c>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1133234</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="4">
+        <v>2</v>
+      </c>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1315418</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="4">
+        <v>2</v>
+      </c>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>212257</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="4">
+        <v>2</v>
+      </c>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>491819</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="4">
+        <v>2</v>
+      </c>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>983246</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="4">
+        <v>2</v>
+      </c>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>760759</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="4">
+        <v>2</v>
+      </c>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>370171</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="4">
+        <v>2</v>
+      </c>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1786506</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="4">
+        <v>2</v>
+      </c>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>213026</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="4">
+        <v>2</v>
+      </c>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1082691</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="4">
+        <v>2</v>
+      </c>
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1970309</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="4">
+        <v>2</v>
+      </c>
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1865172</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="4">
+        <v>2</v>
+      </c>
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1260726</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="4"/>
+      <c r="D58" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="4">
+        <v>2</v>
+      </c>
+      <c r="G58" s="4"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1791115</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F59" s="4">
+        <v>2</v>
+      </c>
+      <c r="G59" s="4"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>418204</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="4">
+        <v>2</v>
+      </c>
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1345212</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="4">
+        <v>2</v>
+      </c>
+      <c r="G61" s="4"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1862365</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="4">
+        <v>2</v>
+      </c>
+      <c r="G62" s="4"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>549796</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="4">
+        <v>2</v>
+      </c>
+      <c r="G63" s="4"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1435978</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="4">
+        <v>2</v>
+      </c>
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1285669</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="4"/>
+      <c r="D65" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="4">
+        <v>2</v>
+      </c>
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="3">
+        <f t="shared" ca="1" si="0"/>
+        <v>1796706</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="4">
+        <v>2</v>
+      </c>
+      <c r="G66" s="4"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="3">
+        <f t="shared" ref="A67:A90" ca="1" si="1">RANDBETWEEN(100000,2000000)</f>
+        <v>194598</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="4"/>
+      <c r="D67" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="4">
+        <v>2</v>
+      </c>
+      <c r="G67" s="4"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1955478</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="4"/>
+      <c r="D68" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="4">
+        <v>2</v>
+      </c>
+      <c r="G68" s="4"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1740183</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="4"/>
+      <c r="D69" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="4">
+        <v>2</v>
+      </c>
+      <c r="G69" s="4"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1627827</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="4"/>
+      <c r="D70" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="4">
+        <v>2</v>
+      </c>
+      <c r="G70" s="4"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>841890</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="4">
+        <v>2</v>
+      </c>
+      <c r="G71" s="4"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1071345</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="4"/>
+      <c r="D72" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="4">
+        <v>2</v>
+      </c>
+      <c r="G72" s="4"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1633983</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="4"/>
+      <c r="D73" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="4">
+        <v>2</v>
+      </c>
+      <c r="G73" s="4"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1901462</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="4"/>
+      <c r="D74" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" s="4">
+        <v>2</v>
+      </c>
+      <c r="G74" s="4"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>676400</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="4"/>
+      <c r="D75" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" s="4">
+        <v>2</v>
+      </c>
+      <c r="G75" s="4"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1015813</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="4"/>
+      <c r="D76" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="4">
+        <v>2</v>
+      </c>
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1713307</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="4">
+        <v>2</v>
+      </c>
+      <c r="G77" s="4"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1071639</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="4">
+        <v>2</v>
+      </c>
+      <c r="G78" s="4"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>401826</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="4"/>
+      <c r="D79" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="4">
+        <v>2</v>
+      </c>
+      <c r="G79" s="4"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1667499</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="4"/>
+      <c r="D80" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="4">
+        <v>2</v>
+      </c>
+      <c r="G80" s="4"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1410070</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="4"/>
+      <c r="D81" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="4">
+        <v>2</v>
+      </c>
+      <c r="G81" s="4"/>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1656324</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="4"/>
+      <c r="D82" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="4">
+        <v>2</v>
+      </c>
+      <c r="G82" s="4"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1012126</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="4"/>
+      <c r="D83" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="4">
+        <v>2</v>
+      </c>
+      <c r="G83" s="4"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>1103349</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="4"/>
+      <c r="D84" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="4">
+        <v>2</v>
+      </c>
+      <c r="G84" s="4"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>460814</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="4"/>
+      <c r="D85" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="4">
+        <v>2</v>
+      </c>
+      <c r="G85" s="4"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>447218</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="4"/>
+      <c r="D86" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="4">
+        <v>2</v>
+      </c>
+      <c r="G86" s="4"/>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>342618</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="4"/>
+      <c r="D87" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" s="4">
+        <v>2</v>
+      </c>
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>259526</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="4"/>
+      <c r="D88" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="4">
+        <v>2</v>
+      </c>
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>147982</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="4"/>
+      <c r="D89" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="4">
+        <v>2</v>
+      </c>
+      <c r="G89" s="4"/>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="3">
+        <f t="shared" ca="1" si="1"/>
+        <v>983209</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="4"/>
+      <c r="D90" s="9">
+        <v>966542232326</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="4">
+        <v>2</v>
+      </c>
+      <c r="G90" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
